--- a/assets/constructions/examples/ctd_ecr.xlsx
+++ b/assets/constructions/examples/ctd_ecr.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:Z6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -539,11 +539,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Б-1-5-НП ГОСТ 8742-75</t>
+          <t>А-2-5-У ГОСТ 8742-75</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -553,21 +573,21 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J2" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K2" t="n">
         <v>5</v>
@@ -605,11 +625,17 @@
           <t>ГОСТ 8742-75</t>
         </is>
       </c>
+      <c r="W2" t="n">
+        <v>5</v>
+      </c>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>А-1-4-НП ЧПУ ГОСТ 8742-75</t>
+          <t>Б-1-5-Н ГОСТ 8742-75</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -619,24 +645,24 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G3" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="n">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="J3" t="n">
         <v>60</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -644,7 +670,7 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>MKG_H:4</t>
+          <t>MKG_H:5</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -671,11 +697,17 @@
           <t>ГОСТ 8742-75</t>
         </is>
       </c>
+      <c r="W3" t="n">
+        <v>5</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>А-1-5-У ГОСТ 8742-75</t>
+          <t>А-2-5-Н ЧПУ ГОСТ 8742-75</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -685,21 +717,21 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G4" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J4" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
@@ -737,11 +769,17 @@
           <t>ГОСТ 8742-75</t>
         </is>
       </c>
+      <c r="W4" t="n">
+        <v>5</v>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Б-1-4-НП ГОСТ 8742-75</t>
+          <t>Б-1-4-У ЧПУ ГОСТ 8742-75</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -751,18 +789,18 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G5" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="J5" t="n">
         <v>60</v>
@@ -803,11 +841,17 @@
           <t>ГОСТ 8742-75</t>
         </is>
       </c>
+      <c r="W5" t="n">
+        <v>5</v>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>А-2-2-Н ЧПУ ГОСТ 8742-75</t>
+          <t>А-2-6-У ГОСТ 8742-75</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -817,24 +861,24 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>160</v>
+        <v>340</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="n">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="J6" t="n">
         <v>30</v>
       </c>
       <c r="K6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -842,7 +886,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>MKG_H:2</t>
+          <t>MKG_H:6</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -869,6 +913,12 @@
           <t>ГОСТ 8742-75</t>
         </is>
       </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
